--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="483">
   <si>
     <t>Filename</t>
   </si>
@@ -811,670 +811,658 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9749,0.0070,0.0058,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.9925,0.0001,0.0001,0.0062</t>
-  </si>
-  <si>
-    <t>0.0020,0.0003,0.0006,0.9987</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
+    <t>0.9585,0.0103,0.0110,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9961,0.0002,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.0162,0.0000,0.0083,0.9812</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
+    <t>0.8850,0.0016,0.1122,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0190,0.0001,0.9913,0.0000</t>
+  </si>
+  <si>
+    <t>0.0907,0.0007,0.9426,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0001,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0075,0.9899,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9131,0.0003,0.0921,0.0006</t>
+  </si>
+  <si>
+    <t>0.7387,0.0012,0.2570,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.1019,0.0002,0.9556,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.9970,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.2950,0.7739,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0691,0.2206,0.5388,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.9992,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9941,0.0032,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9835,0.0036,0.0088,0.0002</t>
+  </si>
+  <si>
+    <t>0.0468,0.9544,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9981,0.0353,0.0000</t>
+  </si>
+  <si>
+    <t>0.0155,0.9181,0.0337,0.0015</t>
+  </si>
+  <si>
+    <t>0.0162,0.0029,0.9714,0.0008</t>
+  </si>
+  <si>
+    <t>0.0152,0.0029,0.9702,0.0008</t>
+  </si>
+  <si>
+    <t>0.0021,0.0000,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0024,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9861,0.0233,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9994,0.0005</t>
+  </si>
+  <si>
+    <t>0.0116,0.8786,0.0003,0.2734</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.1384,0.0000,0.9427,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0024,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9637,0.0510,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0061,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9994,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9976,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9909,0.0004,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.9582,0.0005,0.0241,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.0016,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.5950,0.9883,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.3264,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.0050,0.9970</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0199,0.9977</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0012,0.9991</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9949,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9904,0.8197,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9919,0.9792,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9907,0.7953,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9789,0.0051,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.2725,0.0047,0.7199,0.0003</t>
-  </si>
-  <si>
-    <t>0.0406,0.0004,0.9797,0.0000</t>
-  </si>
-  <si>
-    <t>0.0206,0.0001,0.9908,0.0000</t>
-  </si>
-  <si>
-    <t>0.9464,0.0009,0.0400,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0272,0.9714,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9350,0.0005,0.0399,0.0018</t>
-  </si>
-  <si>
-    <t>0.2745,0.0002,0.7730,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9976,0.0004</t>
-  </si>
-  <si>
-    <t>0.0769,0.0001,0.9664,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.0000,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0384,0.9679,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.7158,0.0318,0.1713,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0022,0.9997,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0021,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0983,0.9308,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0096,0.9551,0.0174,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.0002,0.9961,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.0047,0.9854,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9994,0.0024</t>
-  </si>
-  <si>
-    <t>0.0051,0.8586,0.0013,0.8500</t>
-  </si>
-  <si>
-    <t>0.0007,0.9982,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9997,0.0000</t>
+    <t>0.9965,0.0028,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0013,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0104,0.0011,0.9846,0.0006</t>
+  </si>
+  <si>
+    <t>0.9596,0.0009,0.0209,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9990,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9987,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0117,0.9893,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8262,0.0013,0.1864,0.0005</t>
+  </si>
+  <si>
+    <t>0.2062,0.0002,0.8425,0.0002</t>
+  </si>
+  <si>
+    <t>0.8761,0.0107,0.0574,0.0014</t>
+  </si>
+  <si>
+    <t>0.9633,0.0080,0.0055,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.9882,0.0012,0.5265</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9942,0.9842,0.0000</t>
+  </si>
+  <si>
+    <t>0.5196,0.5485,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.8306,0.1884,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.2023,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8144,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0089,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0009,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1111,0.0011,0.8333,0.0025</t>
+  </si>
+  <si>
+    <t>0.0437,0.0001,0.9692,0.0001</t>
+  </si>
+  <si>
+    <t>0.9818,0.0002,0.0098,0.0005</t>
+  </si>
+  <si>
+    <t>0.1414,0.0000,0.0001,0.9693</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.6811,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0059,0.9922,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.6975,0.5062,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7431,0.0004,0.0004,0.2642</t>
+  </si>
+  <si>
+    <t>0.0008,0.0023,0.9984,0.0008</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0851,0.9438,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9920,0.0018,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.7993,0.0030,0.1267,0.0008</t>
+  </si>
+  <si>
+    <t>0.8299,0.0056,0.1548,0.0002</t>
+  </si>
+  <si>
+    <t>0.9889,0.0039,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9861,0.0066,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9604,0.0622,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5960,0.5298,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8021,0.0009,0.1671,0.0013</t>
+  </si>
+  <si>
+    <t>0.9800,0.0252,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9532,0.0211,0.0165,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9936,0.0036,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0014,0.9969,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0960,0.9902,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9997,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0026,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0027,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0012,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9710,0.0404,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9883,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0013,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0060,0.9976,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.6841,0.0004,0.4529,0.0001</t>
-  </si>
-  <si>
-    <t>0.0100,0.0006,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.0038,0.9944,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9802,0.9618,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.8560,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9942,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0022,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0009,0.9995</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0285,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9946,0.9896,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9448,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9876,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.9691,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0043,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0046,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0010,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9658,0.0586,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9648,0.0007,0.0207,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0075,0.9894,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3952,0.7291,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8109,0.0410,0.0613,0.0021</t>
-  </si>
-  <si>
-    <t>0.8138,0.0002,0.1726,0.0006</t>
-  </si>
-  <si>
-    <t>0.9035,0.0107,0.0385,0.0008</t>
-  </si>
-  <si>
-    <t>0.5070,0.0023,0.4648,0.0023</t>
-  </si>
-  <si>
-    <t>0.0003,0.8207,0.0004,0.9848</t>
-  </si>
-  <si>
-    <t>0.0010,0.9962,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9806,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.1538,0.8987,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9721,0.0360,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.7195,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3258,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0036,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0223,0.9948,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1227,0.0006,0.9060,0.0003</t>
-  </si>
-  <si>
-    <t>0.0138,0.0000,0.9919,0.0000</t>
-  </si>
-  <si>
-    <t>0.9197,0.0028,0.0127,0.0113</t>
-  </si>
-  <si>
-    <t>0.0062,0.0001,0.0000,0.9985</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0002,0.9123,0.9562,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9973,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.1686,0.9092,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0000,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.5136,0.0001,0.0027,0.5292</t>
-  </si>
-  <si>
-    <t>0.0007,0.0021,0.9981,0.0012</t>
-  </si>
-  <si>
-    <t>0.9985,0.0000,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.5798,0.4869,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0004,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9773,0.0080,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.3679,0.0453,0.1559,0.0022</t>
-  </si>
-  <si>
-    <t>0.2245,0.0200,0.7262,0.0006</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9970,0.0008,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9949,0.0036,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.6815,0.4740,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.1866,0.8920,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9603,0.0014,0.0310,0.0003</t>
-  </si>
-  <si>
-    <t>0.9694,0.0511,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0011,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9872,0.0038,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0027,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0066,0.0210,0.9777,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0182,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0140,0.0005,0.9843,0.0002</t>
-  </si>
-  <si>
-    <t>0.2588,0.0011,0.8116,0.0003</t>
-  </si>
-  <si>
-    <t>0.0093,0.0041,0.9795,0.0009</t>
-  </si>
-  <si>
-    <t>0.0353,0.0252,0.8589,0.0005</t>
-  </si>
-  <si>
-    <t>0.0671,0.0236,0.8408,0.0003</t>
-  </si>
-  <si>
-    <t>0.9717,0.0005,0.0438,0.0000</t>
-  </si>
-  <si>
-    <t>0.6221,0.0471,0.0201,0.0512</t>
-  </si>
-  <si>
-    <t>0.0365,0.0003,0.9615,0.0004</t>
-  </si>
-  <si>
-    <t>0.0226,0.9770,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3298,0.7565,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.9945,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0655,0.9543,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9918,0.0006,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9487,0.0003,0.0598,0.0003</t>
-  </si>
-  <si>
-    <t>0.8756,0.0037,0.0178,0.0148</t>
-  </si>
-  <si>
-    <t>0.7108,0.0013,0.2950,0.0011</t>
-  </si>
-  <si>
-    <t>0.9736,0.0002,0.0305,0.0002</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.9965,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0005,0.9959,0.0004</t>
-  </si>
-  <si>
-    <t>0.0085,0.0094,0.9781,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0942,0.9739,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0030,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9839,0.0099,0.0028,0.0027</t>
-  </si>
-  <si>
-    <t>0.9977,0.0019,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0063,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0017,0.9995,0.0007</t>
-  </si>
-  <si>
-    <t>0.1157,0.0217,0.7730,0.0006</t>
-  </si>
-  <si>
-    <t>0.9327,0.0008,0.0288,0.0027</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0451,0.9874,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9981,0.0001</t>
-  </si>
-  <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0004,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0189,0.0067,0.9596,0.0010</t>
-  </si>
-  <si>
-    <t>0.2557,0.0024,0.7512,0.0007</t>
-  </si>
-  <si>
-    <t>0.9831,0.0001,0.0129,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0000,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0015,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0024,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0118,0.0013,0.9845,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0068,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0083,0.9972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0104,0.0027,0.9631,0.0050</t>
-  </si>
-  <si>
-    <t>0.0205,0.0007,0.9695,0.0012</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9958,0.0020</t>
-  </si>
-  <si>
-    <t>0.9823,0.0000,0.0016,0.0080</t>
-  </si>
-  <si>
-    <t>0.0026,0.0048,0.0000,0.9986</t>
-  </si>
-  <si>
-    <t>0.0061,0.0000,0.0000,0.9990</t>
-  </si>
-  <si>
-    <t>0.9961,0.0001,0.0001,0.0015</t>
+    <t>0.0232,0.0025,0.9693,0.0005</t>
+  </si>
+  <si>
+    <t>0.0129,0.0014,0.9881,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0015,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.3835,0.0377,0.4159,0.0003</t>
+  </si>
+  <si>
+    <t>0.0358,0.1615,0.6994,0.0002</t>
+  </si>
+  <si>
+    <t>0.6340,0.0107,0.3825,0.0003</t>
+  </si>
+  <si>
+    <t>0.6183,0.0026,0.3021,0.0029</t>
+  </si>
+  <si>
+    <t>0.6050,0.0011,0.4709,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8712,0.1853,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.5019,0.6537,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0108,0.9873,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.6576,0.3378,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.8754,0.0001,0.1629,0.0003</t>
+  </si>
+  <si>
+    <t>0.9919,0.0012,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.8829,0.0073,0.0717,0.0034</t>
+  </si>
+  <si>
+    <t>0.1703,0.0004,0.8835,0.0005</t>
+  </si>
+  <si>
+    <t>0.0383,0.0003,0.9726,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0028,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0339,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.0099,0.0002,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.1188,0.9317,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9907,0.0044,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9953,0.0023,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9984,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0016,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.9985,0.0006</t>
+  </si>
+  <si>
+    <t>0.0149,0.0273,0.9275,0.0019</t>
+  </si>
+  <si>
+    <t>0.9598,0.0001,0.0360,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.2490,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.0002,0.9933,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.0003,0.9935,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0113,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.9388,0.0049,0.0260,0.0010</t>
+  </si>
+  <si>
+    <t>0.9416,0.0002,0.0597,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0001,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0022,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0014,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0032,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0023,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0213,0.9816,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0021,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0016,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0018,0.9948,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9922,0.0041</t>
+  </si>
+  <si>
+    <t>0.0188,0.0002,0.9845,0.0002</t>
+  </si>
+  <si>
+    <t>0.0080,0.0001,0.9896,0.0010</t>
+  </si>
+  <si>
+    <t>0.9859,0.0003,0.0028,0.0037</t>
+  </si>
+  <si>
+    <t>0.0117,0.0013,0.0000,0.9956</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>0.9968,0.0002,0.0002,0.0003</t>
   </si>
 </sst>
 </file>
@@ -1958,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1972,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1986,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2000,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2028,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2042,7 +2030,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2056,7 +2044,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2070,7 +2058,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2084,7 +2072,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2098,7 +2086,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2112,7 +2100,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2126,7 +2114,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2140,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2154,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2168,7 +2156,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2179,10 +2167,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2196,7 +2184,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2210,7 +2198,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2224,7 +2212,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2238,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2252,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2266,7 +2254,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2277,10 +2265,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2294,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2308,7 +2296,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2322,7 +2310,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2336,7 +2324,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2350,7 +2338,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2364,7 +2352,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2378,7 +2366,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2392,7 +2380,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2406,7 +2394,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2420,7 +2408,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2434,7 +2422,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2448,7 +2436,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2462,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2473,10 +2461,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2490,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2504,7 +2492,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2518,7 +2506,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2532,7 +2520,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2546,7 +2534,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2560,7 +2548,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2574,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2588,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2602,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2616,7 +2604,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2700,7 +2688,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2798,7 +2786,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2812,7 +2800,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2823,10 +2811,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2840,7 +2828,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2854,7 +2842,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2868,7 +2856,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2879,10 +2867,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2896,7 +2884,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2910,7 +2898,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2924,7 +2912,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2938,7 +2926,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2952,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2966,7 +2954,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2980,7 +2968,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2994,7 +2982,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3008,7 +2996,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3022,7 +3010,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3036,7 +3024,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3050,7 +3038,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3064,7 +3052,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3092,7 +3080,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>346</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3120,7 +3108,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>273</v>
+        <v>348</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3134,7 +3122,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3148,7 +3136,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3162,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3176,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3190,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3204,7 +3192,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3218,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3232,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3246,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3260,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3274,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3288,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3302,7 +3290,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3316,7 +3304,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3330,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3344,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3358,7 +3346,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3372,7 +3360,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>359</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3386,7 +3374,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3400,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3414,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>359</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3428,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>280</v>
+        <v>359</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3442,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3456,7 +3444,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3467,10 +3455,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,7 +3472,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3498,7 +3486,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3512,7 +3500,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3526,7 +3514,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3540,7 +3528,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>367</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3554,7 +3542,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>368</v>
+        <v>283</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3582,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3596,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3610,7 +3598,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3624,7 +3612,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3638,7 +3626,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3652,7 +3640,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3666,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3680,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>377</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3694,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3708,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3722,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>380</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3733,10 +3721,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3747,10 +3735,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3764,7 +3752,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3778,7 +3766,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3792,7 +3780,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3806,7 +3794,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3820,7 +3808,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3834,7 +3822,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3848,7 +3836,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3862,7 +3850,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3876,7 +3864,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3890,7 +3878,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3904,7 +3892,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3918,7 +3906,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3932,7 +3920,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3946,7 +3934,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>273</v>
+        <v>372</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3960,7 +3948,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3974,7 +3962,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3985,10 +3973,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4002,7 +3990,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>273</v>
+        <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4016,7 +4004,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4030,7 +4018,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4044,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4055,10 +4043,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4072,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4086,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4100,7 +4088,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4111,10 +4099,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4128,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4142,7 +4130,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>273</v>
+        <v>403</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4156,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>407</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4170,7 +4158,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>346</v>
+        <v>404</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4184,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>273</v>
+        <v>405</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4198,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4212,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4226,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4240,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4254,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4268,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,7 +4270,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4296,7 +4284,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4310,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4324,7 +4312,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4338,7 +4326,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4352,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4366,7 +4354,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4380,7 +4368,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4394,7 +4382,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4408,7 +4396,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4422,7 +4410,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4436,7 +4424,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4450,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4464,7 +4452,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>315</v>
+        <v>422</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4478,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4492,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4506,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4520,7 +4508,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4531,10 +4519,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4548,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4562,7 +4550,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4576,7 +4564,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4587,10 +4575,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4604,7 +4592,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4618,7 +4606,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4629,10 +4617,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4646,7 +4634,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4660,7 +4648,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4674,7 +4662,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4688,7 +4676,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4702,7 +4690,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4716,7 +4704,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4727,10 +4715,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4744,7 +4732,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4758,7 +4746,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4772,7 +4760,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4786,7 +4774,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,7 +4788,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4814,7 +4802,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4828,7 +4816,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4842,7 +4830,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4856,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>376</v>
+        <v>450</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4870,7 +4858,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4884,7 +4872,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4898,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4912,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4926,7 +4914,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4940,7 +4928,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4954,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4968,7 +4956,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4982,7 +4970,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4996,7 +4984,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5010,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>461</v>
+        <v>422</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5024,7 +5012,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5038,7 +5026,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>463</v>
+        <v>423</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5052,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5066,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5077,10 +5065,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5094,7 +5082,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5108,7 +5096,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5122,7 +5110,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5136,7 +5124,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5164,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5178,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5192,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5206,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5220,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>474</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5234,7 +5222,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5248,7 +5236,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5262,7 +5250,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5276,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5290,7 +5278,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5304,7 +5292,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5318,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5332,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5346,7 +5334,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5360,7 +5348,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5374,7 +5362,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5388,7 +5376,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>390</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5402,7 +5390,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5416,7 +5404,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
   <si>
     <t>Filename</t>
   </si>
@@ -808,661 +808,682 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9585,0.0103,0.0110,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9961,0.0002,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.0162,0.0000,0.0083,0.9812</t>
+    <t>0.9748,0.0055,0.0065,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9796,0.0002,0.0002,0.0155</t>
+  </si>
+  <si>
+    <t>0.0022,0.0000,0.0004,0.9987</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.0663,0.0007,0.9478,0.0002</t>
+  </si>
+  <si>
+    <t>0.0055,0.0002,0.9949,0.0002</t>
+  </si>
+  <si>
+    <t>0.6611,0.0002,0.5938,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0004,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.9763,0.0001,0.0286,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0136,0.9863,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9621,0.0003,0.0286,0.0007</t>
+  </si>
+  <si>
+    <t>0.3205,0.0002,0.8065,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0282,0.0000,0.9894,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.6709,0.3899,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7335,0.1199,0.0743,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0066,0.9984,0.0017</t>
+  </si>
+  <si>
+    <t>0.0011,0.9982,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9908,0.0015,0.0035,0.0003</t>
+  </si>
+  <si>
+    <t>0.9880,0.0011,0.0076,0.0002</t>
+  </si>
+  <si>
+    <t>0.0815,0.9350,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0103,0.0000</t>
+  </si>
+  <si>
+    <t>0.0100,0.9734,0.0058,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0696,0.0057,0.8237,0.0062</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9975,0.0007</t>
+  </si>
+  <si>
+    <t>0.0016,0.9141,0.0003,0.8422</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0001,0.0067</t>
+  </si>
+  <si>
+    <t>0.0004,0.9988,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0081,0.0001,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9896,0.0038,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9275,0.9932,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0015,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9981,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7519,0.0002,0.3606,0.0001</t>
+  </si>
+  <si>
+    <t>0.0747,0.0002,0.9563,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0039,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9954,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9845,0.6377,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0474,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9941,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.0053,0.9973</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0005,0.9996</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0004,0.9997</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9949,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9814,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9889,0.9026,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9940,0.9392,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0058,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0027,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0016,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0002,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0006,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.9099,0.0003,0.0753,0.0011</t>
+  </si>
+  <si>
+    <t>0.0051,0.0009,0.9942,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.9935,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2658,0.8179,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.6664,0.0009,0.2954,0.0009</t>
+  </si>
+  <si>
+    <t>0.8752,0.0001,0.1634,0.0002</t>
+  </si>
+  <si>
+    <t>0.6703,0.0023,0.2459,0.0029</t>
+  </si>
+  <si>
+    <t>0.9227,0.0155,0.0095,0.0039</t>
+  </si>
+  <si>
+    <t>0.0001,0.8309,0.0008,0.9815</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9953,0.8124,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2634,0.7728,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.9780,0.0256,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.3344,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9726,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0021,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0023,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3795,0.0036,0.5628,0.0024</t>
+  </si>
+  <si>
+    <t>0.0104,0.0000,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.9466,0.0044,0.0230,0.0012</t>
+  </si>
+  <si>
+    <t>0.0069,0.0000,0.0001,0.9980</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9904,0.3520,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.9903,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.4236,0.7687,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7541,0.0001,0.0023,0.2410</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9992,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0000,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0428,0.9504,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9774,0.0069,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.0438,0.8486,0.0256,0.0039</t>
+  </si>
+  <si>
+    <t>0.9199,0.0113,0.0419,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0003,0.0002</t>
+  </si>
+  <si>
     <t>0.9997,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8850,0.0016,0.1122,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.0003,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0190,0.0001,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0907,0.0007,0.9426,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0075,0.9899,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9131,0.0003,0.0921,0.0006</t>
-  </si>
-  <si>
-    <t>0.7387,0.0012,0.2570,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9985,0.0001</t>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9820,0.0085,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.7096,0.3646,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9849,0.0137,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0017,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.9703,0.0390,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0028,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9658,0.0209,0.0104,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9592,0.0428,0.0058,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0044,0.9925,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3590,0.9928,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.4051,0.0029,0.5665,0.0014</t>
+  </si>
+  <si>
+    <t>0.0590,0.0005,0.9559,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0340,0.0029,0.9599,0.0002</t>
+  </si>
+  <si>
+    <t>0.0291,0.0169,0.9306,0.0001</t>
+  </si>
+  <si>
+    <t>0.7823,0.0017,0.3295,0.0002</t>
+  </si>
+  <si>
+    <t>0.9667,0.0029,0.0092,0.0017</t>
+  </si>
+  <si>
+    <t>0.0244,0.0009,0.9731,0.0004</t>
+  </si>
+  <si>
+    <t>0.0108,0.9883,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7622,0.3272,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.7486,0.3683,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0234,0.9761,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9895,0.0008,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9748,0.0003,0.0244,0.0002</t>
+  </si>
+  <si>
+    <t>0.9815,0.0003,0.0093,0.0009</t>
+  </si>
+  <si>
+    <t>0.9482,0.0023,0.0253,0.0014</t>
+  </si>
+  <si>
+    <t>0.8934,0.0014,0.0878,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9995,0.0002</t>
   </si>
   <si>
     <t>0.0003,0.0002,0.9991,0.0001</t>
   </si>
   <si>
-    <t>0.1019,0.0002,0.9556,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0002,0.9970,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.2950,0.7739,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0691,0.2206,0.5388,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9992,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9941,0.0032,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9835,0.0036,0.0088,0.0002</t>
-  </si>
-  <si>
-    <t>0.0468,0.9544,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9981,0.0353,0.0000</t>
-  </si>
-  <si>
-    <t>0.0155,0.9181,0.0337,0.0015</t>
-  </si>
-  <si>
-    <t>0.0162,0.0029,0.9714,0.0008</t>
-  </si>
-  <si>
-    <t>0.0152,0.0029,0.9702,0.0008</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0024,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9861,0.0233,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9994,0.0005</t>
-  </si>
-  <si>
-    <t>0.0116,0.8786,0.0003,0.2734</t>
-  </si>
-  <si>
-    <t>0.0008,0.9980,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.9986,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.1384,0.0000,0.9427,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0024,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9999,0.0001</t>
+    <t>0.0315,0.0249,0.9291,0.0016</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0078,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0024,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9760,0.0198,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0023,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0012,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0321,0.0113,0.9208,0.0023</t>
+  </si>
+  <si>
+    <t>0.9770,0.0014,0.0084,0.0010</t>
+  </si>
+  <si>
+    <t>0.0256,0.0016,0.9750,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.7956,0.9302,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.9968,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.0067,0.9942,0.0001</t>
+  </si>
+  <si>
+    <t>0.6762,0.0075,0.2322,0.0016</t>
+  </si>
+  <si>
+    <t>0.9656,0.0004,0.0233,0.0006</t>
+  </si>
+  <si>
+    <t>0.9808,0.0008,0.0071,0.0003</t>
   </si>
   <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9637,0.0510,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0061,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9994,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9976,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9909,0.0004,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9582,0.0005,0.0241,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.0016,0.9995,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.5950,0.9883,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.3264,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0050,0.9970</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.0199,0.9977</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.0012,0.9991</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9949,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9904,0.8197,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9919,0.9792,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9907,0.7953,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0028,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0104,0.0011,0.9846,0.0006</t>
-  </si>
-  <si>
-    <t>0.9596,0.0009,0.0209,0.0011</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9990,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9987,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0117,0.9893,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8262,0.0013,0.1864,0.0005</t>
-  </si>
-  <si>
-    <t>0.2062,0.0002,0.8425,0.0002</t>
-  </si>
-  <si>
-    <t>0.8761,0.0107,0.0574,0.0014</t>
-  </si>
-  <si>
-    <t>0.9633,0.0080,0.0055,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.9882,0.0012,0.5265</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9942,0.9842,0.0000</t>
-  </si>
-  <si>
-    <t>0.5196,0.5485,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.8306,0.1884,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
+    <t>0.9976,0.0019,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0059,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0016,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9993,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.2023,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8144,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0089,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0009,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1111,0.0011,0.8333,0.0025</t>
-  </si>
-  <si>
-    <t>0.0437,0.0001,0.9692,0.0001</t>
-  </si>
-  <si>
-    <t>0.9818,0.0002,0.0098,0.0005</t>
-  </si>
-  <si>
-    <t>0.1414,0.0000,0.0001,0.9693</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9964,0.6811,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.9922,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.6975,0.5062,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7431,0.0004,0.0004,0.2642</t>
-  </si>
-  <si>
-    <t>0.0008,0.0023,0.9984,0.0008</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0851,0.9438,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9920,0.0018,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.7993,0.0030,0.1267,0.0008</t>
-  </si>
-  <si>
-    <t>0.8299,0.0056,0.1548,0.0002</t>
-  </si>
-  <si>
-    <t>0.9889,0.0039,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9861,0.0066,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9604,0.0622,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5960,0.5298,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8021,0.0009,0.1671,0.0013</t>
-  </si>
-  <si>
-    <t>0.9800,0.0252,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0006,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9532,0.0211,0.0165,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0036,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0014,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.0012,0.0960,0.9902,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0232,0.0025,0.9693,0.0005</t>
-  </si>
-  <si>
-    <t>0.0129,0.0014,0.9881,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.3835,0.0377,0.4159,0.0003</t>
-  </si>
-  <si>
-    <t>0.0358,0.1615,0.6994,0.0002</t>
-  </si>
-  <si>
-    <t>0.6340,0.0107,0.3825,0.0003</t>
-  </si>
-  <si>
-    <t>0.6183,0.0026,0.3021,0.0029</t>
-  </si>
-  <si>
-    <t>0.6050,0.0011,0.4709,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8712,0.1853,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.5019,0.6537,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0108,0.9873,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.6576,0.3378,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.8754,0.0001,0.1629,0.0003</t>
-  </si>
-  <si>
-    <t>0.9919,0.0012,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.8829,0.0073,0.0717,0.0034</t>
-  </si>
-  <si>
-    <t>0.1703,0.0004,0.8835,0.0005</t>
-  </si>
-  <si>
-    <t>0.0383,0.0003,0.9726,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0028,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0339,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.0099,0.0002,0.9915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.1188,0.9317,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9907,0.0044,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9953,0.0023,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9984,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0016,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0009,0.9985,0.0006</t>
-  </si>
-  <si>
-    <t>0.0149,0.0273,0.9275,0.0019</t>
-  </si>
-  <si>
-    <t>0.9598,0.0001,0.0360,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.2490,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0002,0.9933,0.0004</t>
-  </si>
-  <si>
-    <t>0.0044,0.0003,0.9935,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0113,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.9388,0.0049,0.0260,0.0010</t>
-  </si>
-  <si>
-    <t>0.9416,0.0002,0.0597,0.0003</t>
-  </si>
-  <si>
-    <t>0.9939,0.0001,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0022,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0032,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0023,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0213,0.9816,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0018,0.9948,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9922,0.0041</t>
-  </si>
-  <si>
-    <t>0.0188,0.0002,0.9845,0.0002</t>
-  </si>
-  <si>
-    <t>0.0080,0.0001,0.9896,0.0010</t>
-  </si>
-  <si>
-    <t>0.9859,0.0003,0.0028,0.0037</t>
-  </si>
-  <si>
-    <t>0.0117,0.0013,0.0000,0.9956</t>
-  </si>
-  <si>
-    <t>0.0025,0.0001,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0002,0.0003</t>
+    <t>0.0055,0.0161,0.9748,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.5316,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0011,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.0031,0.9848,0.0035</t>
+  </si>
+  <si>
+    <t>0.2533,0.0013,0.7528,0.0006</t>
+  </si>
+  <si>
+    <t>0.0051,0.0006,0.9900,0.0015</t>
+  </si>
+  <si>
+    <t>0.9484,0.0000,0.0009,0.0452</t>
+  </si>
+  <si>
+    <t>0.0008,0.0015,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0220,0.0000,0.0000,0.9967</t>
+  </si>
+  <si>
+    <t>0.9809,0.0006,0.0008,0.0059</t>
   </si>
 </sst>
 </file>
@@ -1848,7 +1869,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1862,7 +1883,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1876,7 +1897,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1890,7 +1911,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1904,7 +1925,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1918,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1932,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1946,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1960,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1974,7 +1995,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1988,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2002,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2013,10 +2034,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2030,7 +2051,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2041,10 +2062,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2058,7 +2079,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2072,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2086,7 +2107,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2100,7 +2121,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2114,7 +2135,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2128,7 +2149,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2142,7 +2163,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2167,7 +2188,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>285</v>
@@ -2251,7 +2272,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
         <v>291</v>
@@ -2265,7 +2286,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
         <v>292</v>
@@ -2461,7 +2482,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
         <v>306</v>
@@ -2506,7 +2527,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2520,7 +2541,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2534,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2548,7 +2569,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2562,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2576,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2590,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2604,7 +2625,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2618,7 +2639,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2632,7 +2653,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2646,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2660,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2674,7 +2695,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2688,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2702,7 +2723,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2716,7 +2737,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2730,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2744,7 +2765,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2758,7 +2779,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2811,7 +2832,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>329</v>
@@ -3066,7 +3087,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3080,7 +3101,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3108,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3122,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3136,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3150,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3164,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3178,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3192,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3206,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3220,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3234,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3248,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3262,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3276,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3290,7 +3311,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3304,7 +3325,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3318,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3332,7 +3353,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3346,7 +3367,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>304</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3360,7 +3381,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3374,7 +3395,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3388,7 +3409,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3402,7 +3423,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3416,7 +3437,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3430,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3444,7 +3465,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3455,10 +3476,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3472,7 +3493,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3486,7 +3507,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3497,10 +3518,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3514,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3528,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>283</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3542,7 +3563,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>283</v>
+        <v>369</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3556,7 +3577,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3570,7 +3591,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3584,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3598,7 +3619,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3612,7 +3633,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3626,7 +3647,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>372</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3640,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3654,7 +3675,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>272</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3668,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3682,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3696,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3710,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>271</v>
+        <v>379</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3724,7 +3745,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3738,7 +3759,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3752,7 +3773,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3766,7 +3787,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3780,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3794,7 +3815,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3808,7 +3829,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3822,7 +3843,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3836,7 +3857,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3850,7 +3871,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3864,7 +3885,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>386</v>
+        <v>336</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3878,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3889,10 +3910,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3906,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3920,7 +3941,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3934,7 +3955,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3948,7 +3969,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3962,7 +3983,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3976,7 +3997,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3990,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4004,7 +4025,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4018,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4032,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4046,7 +4067,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4060,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4074,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4085,10 +4106,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4102,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4116,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4130,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4144,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>407</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4158,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>404</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4172,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>405</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4186,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4200,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4214,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4228,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4242,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4256,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4267,10 +4288,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4281,10 +4302,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4298,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4312,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4326,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4340,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4354,7 +4375,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4368,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4382,7 +4403,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>418</v>
+        <v>315</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4396,7 +4417,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4410,7 +4431,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4424,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4438,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4452,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4466,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4480,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4494,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4508,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4519,10 +4540,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4536,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4550,7 +4571,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4564,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4575,10 +4596,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4592,7 +4613,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4606,7 +4627,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4620,7 +4641,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4631,10 +4652,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4648,7 +4669,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4662,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4676,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4690,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4704,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4715,10 +4736,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4732,7 +4753,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4746,7 +4767,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4760,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4774,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4788,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4802,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4816,7 +4837,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4830,7 +4851,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4844,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4858,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4872,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4886,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4900,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>272</v>
+        <v>458</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4914,7 +4935,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4928,7 +4949,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4942,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4956,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4970,7 +4991,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4981,10 +5002,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4998,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>422</v>
+        <v>465</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5012,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5026,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>423</v>
+        <v>315</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5040,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5054,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5068,7 +5089,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5082,7 +5103,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5096,7 +5117,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5110,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5124,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5138,7 +5159,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5152,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5166,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5180,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5194,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5208,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>477</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5222,7 +5243,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5236,7 +5257,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5247,10 +5268,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5264,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5278,7 +5299,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5292,7 +5313,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5306,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5320,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5334,7 +5355,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5348,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5362,7 +5383,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5376,7 +5397,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>337</v>
+        <v>389</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5390,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5404,7 +5425,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
